--- a/INTELLEGENT-SYSTEM-DATABASE-TO-EXCEL/ODBC.xlsx
+++ b/INTELLEGENT-SYSTEM-DATABASE-TO-EXCEL/ODBC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\niceadmin\INTELLEGENT-SYSTEM-DATABASE-TO-EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{628428CB-9097-487C-8927-4472D787FA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7485B8A-9EAE-40F4-9E15-9D5FCDDB33B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200" firstSheet="4" activeTab="9" xr2:uid="{505816AB-762D-4C9B-A848-B69AFEA3F1E5}"/>
   </bookViews>
